--- a/data/trans_orig/P36B09-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B09-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de carne en 2007</t>
+          <t>Población según la frecuencia de consumo de carne en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6766</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21219</t>
+          <t>20464</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26387</t>
+          <t>25899</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18268</t>
+          <t>18618</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39668</t>
+          <t>39929</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57769</t>
+          <t>58407</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91054</t>
+          <t>91077</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59750</t>
+          <t>60144</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>96975</t>
+          <t>95165</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>129197</t>
+          <t>128390</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>178263</t>
+          <t>176807</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>411892</t>
+          <t>409238</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>474472</t>
+          <t>472569</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>607907</t>
+          <t>609892</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>680940</t>
+          <t>682592</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1038896</t>
+          <t>1043885</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1137639</t>
+          <t>1137975</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,52%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>421596</t>
+          <t>424471</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>485740</t>
+          <t>489785</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>512955</t>
+          <t>510496</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>582928</t>
+          <t>579445</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>955337</t>
+          <t>955765</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1049635</t>
+          <t>1044782</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,55%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34490</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63961</t>
+          <t>62490</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20658</t>
+          <t>19738</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41601</t>
+          <t>41724</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60364</t>
+          <t>60149</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>95528</t>
+          <t>95869</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17502</t>
+          <t>18246</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14573</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33520</t>
+          <t>33522</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21470</t>
+          <t>22004</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44274</t>
+          <t>45472</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26688</t>
+          <t>27741</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52093</t>
+          <t>52266</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52140</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86348</t>
+          <t>88391</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87431</t>
+          <t>87877</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>130727</t>
+          <t>129978</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>591542</t>
+          <t>594472</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>676819</t>
+          <t>676738</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>646817</t>
+          <t>646146</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>724984</t>
+          <t>721281</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1261479</t>
+          <t>1268060</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1378707</t>
+          <t>1376314</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>791508</t>
+          <t>785024</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>877674</t>
+          <t>867887</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>695724</t>
+          <t>695781</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>775970</t>
+          <t>775679</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1500860</t>
+          <t>1506796</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1624617</t>
+          <t>1622314</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,49%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151684</t>
+          <t>155852</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>203974</t>
+          <t>204202</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59777</t>
+          <t>60495</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>93692</t>
+          <t>97283</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>224181</t>
+          <t>224509</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>284757</t>
+          <t>290647</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15816</t>
+          <t>16288</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>14184</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23279</t>
+          <t>25260</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17112</t>
+          <t>16708</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37136</t>
+          <t>37219</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17104</t>
+          <t>17835</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36202</t>
+          <t>37801</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39612</t>
+          <t>38581</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68124</t>
+          <t>67012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>215729</t>
+          <t>213109</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>263358</t>
+          <t>260761</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>187159</t>
+          <t>187690</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>230267</t>
+          <t>231542</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>411752</t>
+          <t>412343</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>477552</t>
+          <t>476142</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,37%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>214577</t>
+          <t>216472</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>260970</t>
+          <t>264469</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>194750</t>
+          <t>196316</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>239886</t>
+          <t>238885</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>422106</t>
+          <t>425772</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>488541</t>
+          <t>488492</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,57%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32125</t>
+          <t>32051</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59379</t>
+          <t>58491</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>10017</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26924</t>
+          <t>26070</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46215</t>
+          <t>46721</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>76230</t>
+          <t>77356</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18019</t>
+          <t>18849</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41415</t>
+          <t>41723</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32421</t>
+          <t>32642</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57505</t>
+          <t>59839</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56012</t>
+          <t>57683</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91752</t>
+          <t>93821</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>115668</t>
+          <t>115669</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>160949</t>
+          <t>161179</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>147356</t>
+          <t>147757</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>201444</t>
+          <t>199549</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>277365</t>
+          <t>275597</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>348635</t>
+          <t>344688</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1262175</t>
+          <t>1260944</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1372920</t>
+          <t>1366734</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1482745</t>
+          <t>1475639</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1595043</t>
+          <t>1595229</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2769798</t>
+          <t>2778495</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2938413</t>
+          <t>2933484</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,11%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1467319</t>
+          <t>1465369</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1582388</t>
+          <t>1574589</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1441320</t>
+          <t>1439496</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1556047</t>
+          <t>1555289</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2931400</t>
+          <t>2939492</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3102581</t>
+          <t>3100994</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,63%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>236423</t>
+          <t>241293</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>300293</t>
+          <t>307633</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>103632</t>
+          <t>103036</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>149515</t>
+          <t>146338</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>356301</t>
+          <t>357909</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>435253</t>
+          <t>432843</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de carne en 2012</t>
+          <t>Población según la frecuencia de consumo de carne en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5733</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20716</t>
+          <t>20467</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17053</t>
+          <t>17595</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37169</t>
+          <t>38143</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25752</t>
+          <t>26779</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51821</t>
+          <t>52064</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101217</t>
+          <t>103779</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146938</t>
+          <t>151577</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152416</t>
+          <t>154689</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>202903</t>
+          <t>205094</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>271064</t>
+          <t>270106</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>338794</t>
+          <t>339653</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>421868</t>
+          <t>420399</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>486564</t>
+          <t>484857</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>629290</t>
+          <t>627381</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>699557</t>
+          <t>702863</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1068418</t>
+          <t>1067942</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1162460</t>
+          <t>1165155</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,7%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>296636</t>
+          <t>295935</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>355232</t>
+          <t>356704</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>384105</t>
+          <t>382450</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>453502</t>
+          <t>450662</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>691750</t>
+          <t>699267</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>784128</t>
+          <t>788516</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,31%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38959</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67091</t>
+          <t>67338</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34724</t>
+          <t>33700</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>61067</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79763</t>
+          <t>78258</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119691</t>
+          <t>119326</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24624</t>
+          <t>24542</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22423</t>
+          <t>21856</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19837</t>
+          <t>18218</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41385</t>
+          <t>39949</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66176</t>
+          <t>65050</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103446</t>
+          <t>99405</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95197</t>
+          <t>94912</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139264</t>
+          <t>139082</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>169205</t>
+          <t>168016</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>226281</t>
+          <t>226769</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>666994</t>
+          <t>670675</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>758457</t>
+          <t>756831</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>659210</t>
+          <t>659838</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>743119</t>
+          <t>744766</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1347798</t>
+          <t>1354231</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1471557</t>
+          <t>1471136</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,65%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>931272</t>
+          <t>935658</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1024872</t>
+          <t>1023648</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>735760</t>
+          <t>735092</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>820627</t>
+          <t>820578</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1694300</t>
+          <t>1700335</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1822288</t>
+          <t>1824628</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148699</t>
+          <t>145457</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>198903</t>
+          <t>200679</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>118509</t>
+          <t>119290</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>164280</t>
+          <t>165991</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>280188</t>
+          <t>279812</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>349345</t>
+          <t>348730</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>896</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13614</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15522</t>
+          <t>17371</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21998</t>
+          <t>21785</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20364</t>
+          <t>19368</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47179</t>
+          <t>45526</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20597</t>
+          <t>20418</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43946</t>
+          <t>43880</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45869</t>
+          <t>46100</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>80555</t>
+          <t>80607</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>144047</t>
+          <t>142971</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>186798</t>
+          <t>184953</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159360</t>
+          <t>158931</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>203359</t>
+          <t>203267</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>315794</t>
+          <t>313275</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>378322</t>
+          <t>375813</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>208831</t>
+          <t>207542</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>255368</t>
+          <t>253435</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>189817</t>
+          <t>191605</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>235411</t>
+          <t>236684</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>412691</t>
+          <t>411287</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>476045</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,87%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35503</t>
+          <t>34198</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60859</t>
+          <t>60529</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19443</t>
+          <t>18596</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41022</t>
+          <t>40294</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>59285</t>
+          <t>60604</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>93111</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20412</t>
+          <t>20118</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44005</t>
+          <t>43018</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,39 +5752,39 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>45541</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>32142</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>61461</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>1,29%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>45541</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>32398</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>60343</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58664</t>
+          <t>59266</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96740</t>
+          <t>94500</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>204194</t>
+          <t>205782</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>269144</t>
+          <t>270232</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>287321</t>
+          <t>292568</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>358291</t>
+          <t>361409</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>510621</t>
+          <t>519230</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>609646</t>
+          <t>613755</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1271604</t>
+          <t>1267771</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1391890</t>
+          <t>1390722</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1490968</t>
+          <t>1485953</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1607316</t>
+          <t>1605388</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2799024</t>
+          <t>2795575</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2971626</t>
+          <t>2961180</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,64%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1472542</t>
+          <t>1472946</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1595631</t>
+          <t>1598428</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1349093</t>
+          <t>1348528</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1469281</t>
+          <t>1472007</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2863868</t>
+          <t>2856653</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3035568</t>
+          <t>3033764</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,69%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>240876</t>
+          <t>238060</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>305475</t>
+          <t>303737</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>188359</t>
+          <t>186717</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>244146</t>
+          <t>243997</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>439633</t>
+          <t>443679</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>528956</t>
+          <t>528425</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de carne en 2016</t>
+          <t>Población según la frecuencia de consumo de carne en 2016 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>14031</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20110</t>
+          <t>19681</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11516</t>
+          <t>10940</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29644</t>
+          <t>28207</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>13373</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31190</t>
+          <t>31406</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39855</t>
+          <t>40446</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69454</t>
+          <t>70034</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56440</t>
+          <t>56167</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90873</t>
+          <t>92907</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>224896</t>
+          <t>223914</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>274085</t>
+          <t>275397</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>372907</t>
+          <t>370753</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>435416</t>
+          <t>437957</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>614783</t>
+          <t>610548</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>696046</t>
+          <t>694048</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>313864</t>
+          <t>316075</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>367368</t>
+          <t>368274</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>339836</t>
+          <t>338778</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>402802</t>
+          <t>403854</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>670945</t>
+          <t>670080</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>756956</t>
+          <t>752641</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,19%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>112107</t>
+          <t>110151</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154714</t>
+          <t>151855</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>133744</t>
+          <t>130621</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>179215</t>
+          <t>178498</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>252686</t>
+          <t>253842</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>314517</t>
+          <t>315536</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,11%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17460</t>
+          <t>17924</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9963</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28738</t>
+          <t>27478</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17710</t>
+          <t>17072</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40517</t>
+          <t>39238</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40554</t>
+          <t>41345</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71122</t>
+          <t>73470</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53286</t>
+          <t>52317</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86974</t>
+          <t>86175</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103026</t>
+          <t>103733</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>149126</t>
+          <t>147728</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>664685</t>
+          <t>664352</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>754867</t>
+          <t>757576</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>730331</t>
+          <t>737870</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>819046</t>
+          <t>826246</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1424890</t>
+          <t>1425069</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1552416</t>
+          <t>1549253</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,25%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>953964</t>
+          <t>952850</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1053001</t>
+          <t>1045007</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>787414</t>
+          <t>782124</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>879824</t>
+          <t>872190</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1769449</t>
+          <t>1766110</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1894953</t>
+          <t>1892151</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,71%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>262841</t>
+          <t>262348</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>329402</t>
+          <t>327932</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>258061</t>
+          <t>258655</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>321932</t>
+          <t>322662</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>535077</t>
+          <t>541211</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>626072</t>
+          <t>629180</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11129</t>
+          <t>12128</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22181</t>
+          <t>21946</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28032</t>
+          <t>27260</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15270</t>
+          <t>14750</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36960</t>
+          <t>36941</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17319</t>
+          <t>17496</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38834</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38225</t>
+          <t>36617</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68579</t>
+          <t>69294</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>177050</t>
+          <t>175803</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>221510</t>
+          <t>224006</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>199337</t>
+          <t>198298</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>244509</t>
+          <t>244487</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>388116</t>
+          <t>386055</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>454068</t>
+          <t>454254</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,7%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>227620</t>
+          <t>224357</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>274311</t>
+          <t>273055</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>204805</t>
+          <t>204495</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>252038</t>
+          <t>253703</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>444688</t>
+          <t>444211</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>512249</t>
+          <t>512080</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,0%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49211</t>
+          <t>48946</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>80973</t>
+          <t>81990</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44338</t>
+          <t>44820</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>72174</t>
+          <t>72608</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>98789</t>
+          <t>100565</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>142735</t>
+          <t>141816</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13688</t>
+          <t>13677</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33078</t>
+          <t>32834</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28854</t>
+          <t>29458</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54844</t>
+          <t>55411</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49820</t>
+          <t>46286</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80401</t>
+          <t>79002</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>81781</t>
+          <t>80403</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>121988</t>
+          <t>120148</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>123779</t>
+          <t>122657</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>172133</t>
+          <t>171688</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>215160</t>
+          <t>218153</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>281823</t>
+          <t>280049</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1101263</t>
+          <t>1103422</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1214279</t>
+          <t>1217327</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1338378</t>
+          <t>1350366</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1460190</t>
+          <t>1467063</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2478723</t>
+          <t>2481559</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2643799</t>
+          <t>2644019</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1533880</t>
+          <t>1531279</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1652901</t>
+          <t>1651209</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1368092</t>
+          <t>1377306</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1492366</t>
+          <t>1492832</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2938746</t>
+          <t>2943211</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3108634</t>
+          <t>3107075</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,14%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>450108</t>
+          <t>446110</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>535388</t>
+          <t>529950</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>456148</t>
+          <t>458740</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>542355</t>
+          <t>543057</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>933237</t>
+          <t>927153</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1048895</t>
+          <t>1050384</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B09-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B09-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20464</t>
+          <t>21638</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25899</t>
+          <t>25522</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18618</t>
+          <t>18379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>40138</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58407</t>
+          <t>58835</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91077</t>
+          <t>90204</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60144</t>
+          <t>59899</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95165</t>
+          <t>94388</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128390</t>
+          <t>126625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>176807</t>
+          <t>176777</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>409238</t>
+          <t>412128</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>472569</t>
+          <t>473219</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>609892</t>
+          <t>607175</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>682592</t>
+          <t>679137</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1043885</t>
+          <t>1040893</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1137975</t>
+          <t>1138316</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,54%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>424471</t>
+          <t>424186</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>489785</t>
+          <t>486990</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>510496</t>
+          <t>512616</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>579445</t>
+          <t>583580</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>955765</t>
+          <t>951842</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1044782</t>
+          <t>1052482</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,88%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>35048</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62490</t>
+          <t>61878</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19738</t>
+          <t>20820</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41724</t>
+          <t>42179</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60149</t>
+          <t>60778</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>95869</t>
+          <t>95273</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18246</t>
+          <t>18329</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14680</t>
+          <t>14041</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33522</t>
+          <t>32352</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22004</t>
+          <t>22502</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45472</t>
+          <t>45784</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27741</t>
+          <t>27683</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52266</t>
+          <t>52096</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>54072</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88391</t>
+          <t>87700</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87877</t>
+          <t>89594</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>129978</t>
+          <t>128865</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>594472</t>
+          <t>593894</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>676738</t>
+          <t>674302</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>646146</t>
+          <t>645956</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>721281</t>
+          <t>724920</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1268060</t>
+          <t>1267873</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1376314</t>
+          <t>1380616</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,12%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>785024</t>
+          <t>788470</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>867887</t>
+          <t>871407</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>695781</t>
+          <t>695994</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>775679</t>
+          <t>770927</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1506796</t>
+          <t>1503335</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1622314</t>
+          <t>1616905</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>155852</t>
+          <t>153155</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>204202</t>
+          <t>205522</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60495</t>
+          <t>58744</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97283</t>
+          <t>96423</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>224509</t>
+          <t>225570</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>290647</t>
+          <t>286690</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16288</t>
+          <t>14480</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14184</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25260</t>
+          <t>24209</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16708</t>
+          <t>16857</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37219</t>
+          <t>39256</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17835</t>
+          <t>17041</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37801</t>
+          <t>37420</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38581</t>
+          <t>39147</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67012</t>
+          <t>68141</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>213109</t>
+          <t>211069</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>260761</t>
+          <t>258501</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>187690</t>
+          <t>187827</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>231542</t>
+          <t>231001</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>412343</t>
+          <t>413419</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>476142</t>
+          <t>476510</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,41%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>216472</t>
+          <t>214253</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>264469</t>
+          <t>261282</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>196316</t>
+          <t>195945</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>238885</t>
+          <t>239475</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>425772</t>
+          <t>422297</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>488492</t>
+          <t>487048</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,43%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32051</t>
+          <t>32464</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58491</t>
+          <t>59726</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10017</t>
+          <t>9845</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26070</t>
+          <t>27757</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46721</t>
+          <t>45944</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77356</t>
+          <t>77427</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18849</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41723</t>
+          <t>42088</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32642</t>
+          <t>31570</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59839</t>
+          <t>59394</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57683</t>
+          <t>57383</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93821</t>
+          <t>91798</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>115669</t>
+          <t>115978</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>161179</t>
+          <t>162677</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>147757</t>
+          <t>149260</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>199549</t>
+          <t>199485</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>275597</t>
+          <t>277076</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>344688</t>
+          <t>343763</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1260944</t>
+          <t>1257220</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1366734</t>
+          <t>1367907</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1475639</t>
+          <t>1472361</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1595229</t>
+          <t>1595481</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2778495</t>
+          <t>2773517</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2933484</t>
+          <t>2935532</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,14%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1465369</t>
+          <t>1464474</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1574589</t>
+          <t>1577905</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1439496</t>
+          <t>1442695</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1555289</t>
+          <t>1557350</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2939492</t>
+          <t>2939485</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3100994</t>
+          <t>3103091</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,66%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>241293</t>
+          <t>236684</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>307633</t>
+          <t>301058</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>103036</t>
+          <t>103143</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>146338</t>
+          <t>147498</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>357909</t>
+          <t>355208</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>432843</t>
+          <t>428049</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20467</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17595</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38143</t>
+          <t>37088</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26779</t>
+          <t>26017</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52064</t>
+          <t>52244</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103779</t>
+          <t>103899</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>151577</t>
+          <t>147210</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>154689</t>
+          <t>154364</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>205094</t>
+          <t>205594</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>270106</t>
+          <t>271864</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>339653</t>
+          <t>339317</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>420399</t>
+          <t>422095</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>484857</t>
+          <t>486146</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>627381</t>
+          <t>627309</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>702863</t>
+          <t>701397</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1067942</t>
+          <t>1073057</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1165155</t>
+          <t>1167940</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,82%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>295935</t>
+          <t>296629</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>356704</t>
+          <t>358651</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>382450</t>
+          <t>381020</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>450662</t>
+          <t>452335</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>699267</t>
+          <t>696940</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>788516</t>
+          <t>785417</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,18%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38959</t>
+          <t>37682</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67338</t>
+          <t>66136</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33700</t>
+          <t>34238</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61067</t>
+          <t>60442</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>78258</t>
+          <t>76672</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119326</t>
+          <t>118493</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24542</t>
+          <t>23848</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7916</t>
+          <t>7799</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21856</t>
+          <t>22675</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18218</t>
+          <t>19134</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39949</t>
+          <t>40732</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65050</t>
+          <t>65107</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99405</t>
+          <t>100552</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>96367</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139082</t>
+          <t>140272</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168016</t>
+          <t>171045</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>226769</t>
+          <t>228462</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>670675</t>
+          <t>665861</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>756831</t>
+          <t>755486</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>659838</t>
+          <t>661734</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>744766</t>
+          <t>747421</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1354231</t>
+          <t>1350130</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1471136</t>
+          <t>1472298</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,68%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>935658</t>
+          <t>933786</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1023648</t>
+          <t>1025601</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>735092</t>
+          <t>737796</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>820578</t>
+          <t>825071</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1700335</t>
+          <t>1699509</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1824628</t>
+          <t>1820451</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,06%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>145457</t>
+          <t>148838</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200679</t>
+          <t>197831</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119290</t>
+          <t>117291</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165991</t>
+          <t>164586</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>279812</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348730</t>
+          <t>351198</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>907</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>14852</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17371</t>
+          <t>17158</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21785</t>
+          <t>21612</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19368</t>
+          <t>20483</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45526</t>
+          <t>45039</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20418</t>
+          <t>20727</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43880</t>
+          <t>41984</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46100</t>
+          <t>46234</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>80607</t>
+          <t>80539</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>142971</t>
+          <t>142922</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>184953</t>
+          <t>187061</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>158931</t>
+          <t>157139</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>203267</t>
+          <t>202656</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>313275</t>
+          <t>314189</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>375813</t>
+          <t>379435</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>207542</t>
+          <t>209064</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>253435</t>
+          <t>255150</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>191605</t>
+          <t>191539</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>236684</t>
+          <t>235856</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>411287</t>
+          <t>408897</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>476045</t>
+          <t>474913</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,75%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34198</t>
+          <t>33858</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60529</t>
+          <t>59933</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18596</t>
+          <t>18595</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40294</t>
+          <t>41244</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>60604</t>
+          <t>60162</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>94264</t>
+          <t>93031</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20118</t>
+          <t>19919</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43018</t>
+          <t>43977</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32142</t>
+          <t>32473</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61461</t>
+          <t>61519</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59266</t>
+          <t>59879</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>94500</t>
+          <t>98303</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>205782</t>
+          <t>206046</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>270232</t>
+          <t>269756</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>292568</t>
+          <t>292479</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>361409</t>
+          <t>361162</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>519230</t>
+          <t>515054</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>613755</t>
+          <t>609923</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1267771</t>
+          <t>1265789</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1390722</t>
+          <t>1384730</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1485953</t>
+          <t>1484311</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1605388</t>
+          <t>1603497</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2795575</t>
+          <t>2786080</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2961180</t>
+          <t>2956583</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,57%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1472946</t>
+          <t>1478123</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1598428</t>
+          <t>1603785</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1348528</t>
+          <t>1346572</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1472007</t>
+          <t>1464294</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2856653</t>
+          <t>2856499</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3033764</t>
+          <t>3028393</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,61%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>238060</t>
+          <t>241741</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>303737</t>
+          <t>303749</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>186717</t>
+          <t>187368</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>243997</t>
+          <t>245807</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>443679</t>
+          <t>438815</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>528425</t>
+          <t>529139</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14031</t>
+          <t>15135</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19681</t>
+          <t>19309</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>10563</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28207</t>
+          <t>27720</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13373</t>
+          <t>12922</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31406</t>
+          <t>31219</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40446</t>
+          <t>40147</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70034</t>
+          <t>68855</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56167</t>
+          <t>57662</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92907</t>
+          <t>91347</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>223914</t>
+          <t>223601</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>275397</t>
+          <t>273468</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>370753</t>
+          <t>372712</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>437957</t>
+          <t>438073</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>610548</t>
+          <t>614686</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>694048</t>
+          <t>695780</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,92%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>316075</t>
+          <t>315611</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>368274</t>
+          <t>367806</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>338778</t>
+          <t>338519</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>403854</t>
+          <t>404882</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>670080</t>
+          <t>668942</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>752641</t>
+          <t>753948</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,26%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>110151</t>
+          <t>110468</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>151855</t>
+          <t>151298</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>130621</t>
+          <t>128838</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>178498</t>
+          <t>177018</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>253842</t>
+          <t>255430</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>315536</t>
+          <t>317459</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17924</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>9766</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27478</t>
+          <t>27764</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17072</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39238</t>
+          <t>40304</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41345</t>
+          <t>41341</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73470</t>
+          <t>72999</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52317</t>
+          <t>54443</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86175</t>
+          <t>86797</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103733</t>
+          <t>101049</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>147728</t>
+          <t>145837</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>664352</t>
+          <t>668362</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>757576</t>
+          <t>752138</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>737870</t>
+          <t>735188</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>826246</t>
+          <t>823721</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1425069</t>
+          <t>1427629</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1549253</t>
+          <t>1553288</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>952850</t>
+          <t>958190</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1045007</t>
+          <t>1043473</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>782124</t>
+          <t>788099</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>872190</t>
+          <t>879886</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1766110</t>
+          <t>1768119</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1892151</t>
+          <t>1892690</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,73%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>262348</t>
+          <t>261673</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>327932</t>
+          <t>326920</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>258655</t>
+          <t>258103</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>322662</t>
+          <t>320243</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>541211</t>
+          <t>538093</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>629180</t>
+          <t>624793</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12128</t>
+          <t>12375</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21946</t>
+          <t>22856</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10632</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27260</t>
+          <t>28085</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14750</t>
+          <t>15253</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36941</t>
+          <t>36249</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17496</t>
+          <t>17844</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36617</t>
+          <t>38467</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69294</t>
+          <t>68566</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>175803</t>
+          <t>177115</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>224006</t>
+          <t>221123</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>198298</t>
+          <t>197783</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>244487</t>
+          <t>243902</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386055</t>
+          <t>389740</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>454254</t>
+          <t>454447</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,71%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>224357</t>
+          <t>226379</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>273055</t>
+          <t>273702</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>204495</t>
+          <t>202924</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>253703</t>
+          <t>251275</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>444211</t>
+          <t>445937</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>512080</t>
+          <t>511210</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,92%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48946</t>
+          <t>50252</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>81990</t>
+          <t>80154</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44820</t>
+          <t>43719</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>72608</t>
+          <t>72386</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>100565</t>
+          <t>100985</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>141816</t>
+          <t>145032</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13677</t>
+          <t>13040</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32834</t>
+          <t>31512</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29458</t>
+          <t>28805</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55411</t>
+          <t>54927</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46286</t>
+          <t>46625</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79002</t>
+          <t>79339</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>80403</t>
+          <t>81241</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>120148</t>
+          <t>123254</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>122657</t>
+          <t>125722</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>171688</t>
+          <t>173501</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>218153</t>
+          <t>220015</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>280049</t>
+          <t>284659</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1103422</t>
+          <t>1106343</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1217327</t>
+          <t>1222004</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1350366</t>
+          <t>1346450</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1467063</t>
+          <t>1467237</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2481559</t>
+          <t>2469170</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2644019</t>
+          <t>2640332</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,36%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1531279</t>
+          <t>1532353</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1651209</t>
+          <t>1648253</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1377306</t>
+          <t>1372266</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1492832</t>
+          <t>1492229</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2943211</t>
+          <t>2942653</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3107075</t>
+          <t>3111409</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,21%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>446110</t>
+          <t>449203</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>529950</t>
+          <t>529297</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>458740</t>
+          <t>455637</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>543057</t>
+          <t>541500</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>927153</t>
+          <t>929393</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1050384</t>
+          <t>1054590</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
